--- a/exports/trend_1d/EICHERMOT_full_report.xlsx
+++ b/exports/trend_1d/EICHERMOT_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q94"/>
+  <dimension ref="A1:U94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.67</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>1558.75</v>
+        <v>1511.55</v>
       </c>
       <c r="I2" t="n">
         <v>1532.814477352753</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.04</v>
+        <v>-0.08</v>
       </c>
       <c r="L2" t="n">
         <v>1.86</v>
@@ -555,7 +578,7 @@
         <v>0.47</v>
       </c>
       <c r="N2" t="n">
-        <v>2.47</v>
+        <v>3.03</v>
       </c>
       <c r="O2" t="n">
         <v>1.98</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>10.37</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42051</v>
+        <v>42053</v>
       </c>
       <c r="H3" t="n">
-        <v>1605.1</v>
+        <v>1694.75</v>
       </c>
       <c r="I3" t="n">
         <v>1659.817370791176</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.19</v>
+        <v>-12.12</v>
       </c>
       <c r="L3" t="n">
-        <v>11.62</v>
+        <v>12.78</v>
       </c>
       <c r="M3" t="n">
         <v>2.17</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>13.8</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42111</v>
+        <v>42114</v>
       </c>
       <c r="H4" t="n">
-        <v>1531.1</v>
+        <v>1476.2</v>
       </c>
       <c r="I4" t="n">
         <v>1513.085861890747</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.66</v>
+        <v>-12.9</v>
       </c>
       <c r="L4" t="n">
-        <v>11.19</v>
+        <v>13.67</v>
       </c>
       <c r="M4" t="n">
         <v>3.19</v>
       </c>
       <c r="N4" t="n">
-        <v>3.32</v>
+        <v>3.59</v>
       </c>
       <c r="O4" t="n">
         <v>5.59</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>10.9</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42131</v>
+        <v>42132</v>
       </c>
       <c r="H5" t="n">
-        <v>1480.7</v>
+        <v>1578.1</v>
       </c>
       <c r="I5" t="n">
         <v>1574.195458982945</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3</v>
+        <v>-6.9</v>
       </c>
       <c r="L5" t="n">
-        <v>6.5</v>
+        <v>7.64</v>
       </c>
       <c r="M5" t="n">
         <v>1.65</v>
       </c>
       <c r="N5" t="n">
-        <v>2.74</v>
+        <v>6.58</v>
       </c>
       <c r="O5" t="n">
         <v>-3.59</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>14.19</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42163</v>
+        <v>42164</v>
       </c>
       <c r="H6" t="n">
-        <v>1728.25</v>
+        <v>1710.85</v>
       </c>
       <c r="I6" t="n">
         <v>1713.277061156411</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K6" t="n">
-        <v>9.51</v>
+        <v>8.41</v>
       </c>
       <c r="L6" t="n">
         <v>6.85</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>11.63</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42171</v>
+        <v>42172</v>
       </c>
       <c r="H7" t="n">
-        <v>1845.2</v>
+        <v>1928.9</v>
       </c>
       <c r="I7" t="n">
         <v>1909.811037578573</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.85</v>
+        <v>-12.75</v>
       </c>
       <c r="L7" t="n">
-        <v>8.279999999999999</v>
+        <v>13.98</v>
       </c>
       <c r="M7" t="n">
         <v>1.9</v>
       </c>
       <c r="N7" t="n">
-        <v>3.58</v>
+        <v>4.54</v>
       </c>
       <c r="O7" t="n">
         <v>-1.01</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.06</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42209</v>
+        <v>42212</v>
       </c>
       <c r="H8" t="n">
-        <v>2011.4</v>
+        <v>1934.8</v>
       </c>
       <c r="I8" t="n">
         <v>2006.630087204781</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K8" t="n">
-        <v>4.28</v>
+        <v>0.31</v>
       </c>
       <c r="L8" t="n">
         <v>3.85</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.82</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42230</v>
+        <v>42233</v>
       </c>
       <c r="H9" t="n">
-        <v>2060.05</v>
+        <v>2066.5</v>
       </c>
       <c r="I9" t="n">
         <v>2063.496382648901</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.47</v>
+        <v>-6.81</v>
       </c>
       <c r="L9" t="n">
         <v>7.34</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H10" t="n">
-        <v>2046.5</v>
+        <v>1858.55</v>
       </c>
       <c r="I10" t="n">
         <v>1956.944088540378</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.97</v>
+        <v>-10.06</v>
       </c>
       <c r="L10" t="n">
-        <v>1.77</v>
+        <v>13.76</v>
       </c>
       <c r="M10" t="n">
-        <v>0.57</v>
+        <v>2.44</v>
       </c>
       <c r="N10" t="n">
-        <v>2.63</v>
+        <v>9.18</v>
       </c>
       <c r="O10" t="n">
         <v>0.31</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>14.32</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42368</v>
+        <v>42369</v>
       </c>
       <c r="H11" t="n">
-        <v>1653</v>
+        <v>1685.55</v>
       </c>
       <c r="I11" t="n">
         <v>1677.986557736541</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K11" t="n">
-        <v>11.06</v>
+        <v>9.31</v>
       </c>
       <c r="L11" t="n">
         <v>7.42</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>7.3</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H12" t="n">
-        <v>1698.8</v>
+        <v>1624.1</v>
       </c>
       <c r="I12" t="n">
         <v>1638.222596937769</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>0.79</v>
+        <v>-3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.86</v>
+        <v>4.77</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.79</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.97</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>12.27</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42404</v>
+        <v>42405</v>
       </c>
       <c r="H13" t="n">
-        <v>1689.45</v>
+        <v>1811.9</v>
       </c>
       <c r="I13" t="n">
         <v>1727.382599583198</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.02</v>
+        <v>-11.56</v>
       </c>
       <c r="L13" t="n">
-        <v>7.12</v>
+        <v>13.6</v>
       </c>
       <c r="M13" t="n">
         <v>2.14</v>
       </c>
       <c r="N13" t="n">
-        <v>5.92</v>
+        <v>7.25</v>
       </c>
       <c r="O13" t="n">
         <v>-4.4</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>13.84</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42445</v>
+        <v>42446</v>
       </c>
       <c r="H14" t="n">
-        <v>1869.35</v>
+        <v>1803.6</v>
       </c>
       <c r="I14" t="n">
         <v>1855.112761535276</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K14" t="n">
-        <v>3.17</v>
+        <v>-0.46</v>
       </c>
       <c r="L14" t="n">
         <v>6.74</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>11.2</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42472</v>
+        <v>42473</v>
       </c>
       <c r="H15" t="n">
-        <v>1955.8</v>
+        <v>1989.65</v>
       </c>
       <c r="I15" t="n">
         <v>1986.621997156706</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.44</v>
+        <v>-10.32</v>
       </c>
       <c r="L15" t="n">
-        <v>8.67</v>
+        <v>10.71</v>
       </c>
       <c r="M15" t="n">
         <v>0.89</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>8.1</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42502</v>
+        <v>42503</v>
       </c>
       <c r="H16" t="n">
-        <v>1975.3</v>
+        <v>1899.3</v>
       </c>
       <c r="I16" t="n">
         <v>1901.253142219555</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.72</v>
+        <v>-4.54</v>
       </c>
       <c r="L16" t="n">
-        <v>3.43</v>
+        <v>7.62</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.32</v>
       </c>
       <c r="N16" t="n">
-        <v>1.29</v>
+        <v>3.85</v>
       </c>
       <c r="O16" t="n">
         <v>1.73</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42552</v>
+        <v>42555</v>
       </c>
       <c r="H17" t="n">
-        <v>1915.5</v>
+        <v>1949.2</v>
       </c>
       <c r="I17" t="n">
         <v>1935.368686680916</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.85</v>
+        <v>-2.63</v>
       </c>
       <c r="L17" t="n">
-        <v>2.95</v>
+        <v>3.41</v>
       </c>
       <c r="M17" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
         <v>2.44</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.63</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42670</v>
+        <v>42671</v>
       </c>
       <c r="H18" t="n">
-        <v>2449.2</v>
+        <v>2402</v>
       </c>
       <c r="I18" t="n">
         <v>2403.343395497865</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K18" t="n">
-        <v>25.65</v>
+        <v>23.23</v>
       </c>
       <c r="L18" t="n">
         <v>1.24</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.99</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42710</v>
+        <v>42711</v>
       </c>
       <c r="H19" t="n">
-        <v>2245.75</v>
+        <v>2338.2</v>
       </c>
       <c r="I19" t="n">
         <v>2335.700547658027</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K19" t="n">
-        <v>6.5</v>
+        <v>2.66</v>
       </c>
       <c r="L19" t="n">
         <v>6.25</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>13.24</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42727</v>
+        <v>42730</v>
       </c>
       <c r="H20" t="n">
-        <v>2092.2</v>
+        <v>2027.3</v>
       </c>
       <c r="I20" t="n">
         <v>2073.016407587177</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>-10.52</v>
+        <v>-13.3</v>
       </c>
       <c r="L20" t="n">
-        <v>11.09</v>
+        <v>13.49</v>
       </c>
       <c r="M20" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
         <v>4.12</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>11.31</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42740</v>
+        <v>42741</v>
       </c>
       <c r="H21" t="n">
-        <v>2232.45</v>
+        <v>2271.75</v>
       </c>
       <c r="I21" t="n">
         <v>2254.071820943574</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.12</v>
+        <v>-12.06</v>
       </c>
       <c r="L21" t="n">
-        <v>12.7</v>
+        <v>12.72</v>
       </c>
       <c r="M21" t="n">
         <v>2.74</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>8.26</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42796</v>
+        <v>42797</v>
       </c>
       <c r="H22" t="n">
-        <v>2344.9</v>
+        <v>2308.95</v>
       </c>
       <c r="I22" t="n">
         <v>2332.592088909121</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K22" t="n">
-        <v>3.22</v>
+        <v>1.64</v>
       </c>
       <c r="L22" t="n">
         <v>2.39</v>
       </c>
       <c r="M22" t="n">
-        <v>0.41</v>
+        <v>0.85</v>
       </c>
       <c r="N22" t="n">
         <v>2.23</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.27</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>42811</v>
+        <v>42814</v>
       </c>
       <c r="H23" t="n">
-        <v>2469.15</v>
+        <v>2509.95</v>
       </c>
       <c r="I23" t="n">
         <v>2489.983103583546</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.94</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>7.36</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>3.61</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>7.11</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>42905</v>
+        <v>42906</v>
       </c>
       <c r="H24" t="n">
-        <v>2844.5</v>
+        <v>2791.75</v>
       </c>
       <c r="I24" t="n">
         <v>2793.897963237949</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K24" t="n">
-        <v>13.33</v>
+        <v>11.23</v>
       </c>
       <c r="L24" t="n">
         <v>4.3</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>7.35</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>42934</v>
+        <v>42935</v>
       </c>
       <c r="H25" t="n">
-        <v>2859.85</v>
+        <v>2921.5</v>
       </c>
       <c r="I25" t="n">
         <v>2876.067961052579</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.44</v>
+        <v>-4.65</v>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>4.92</v>
       </c>
       <c r="M25" t="n">
         <v>0.96</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.3</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H26" t="n">
-        <v>3082.7</v>
+        <v>3047</v>
       </c>
       <c r="I26" t="n">
         <v>3058.767164098298</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K26" t="n">
-        <v>5.52</v>
+        <v>4.3</v>
       </c>
       <c r="L26" t="n">
         <v>3.53</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>7.45</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43035</v>
+        <v>43038</v>
       </c>
       <c r="H27" t="n">
-        <v>3181.15</v>
+        <v>3237.1</v>
       </c>
       <c r="I27" t="n">
         <v>3229.730050704993</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.4</v>
+        <v>-6.24</v>
       </c>
       <c r="L27" t="n">
-        <v>5.26</v>
+        <v>6.66</v>
       </c>
       <c r="M27" t="n">
         <v>1.88</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>6</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43048</v>
+        <v>43049</v>
       </c>
       <c r="H28" t="n">
-        <v>3085.35</v>
+        <v>3055.15</v>
       </c>
       <c r="I28" t="n">
         <v>3074.022626035491</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.69</v>
+        <v>-5.62</v>
       </c>
       <c r="L28" t="n">
-        <v>5.47</v>
+        <v>6.18</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>6.19</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43087</v>
+        <v>43088</v>
       </c>
       <c r="H29" t="n">
-        <v>2990.95</v>
+        <v>3082.35</v>
       </c>
       <c r="I29" t="n">
         <v>3040.850195875876</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K29" t="n">
-        <v>2.1</v>
+        <v>-0.89</v>
       </c>
       <c r="L29" t="n">
         <v>1.79</v>
@@ -2094,7 +2441,7 @@
         <v>1.15</v>
       </c>
       <c r="N29" t="n">
-        <v>2.57</v>
+        <v>3.06</v>
       </c>
       <c r="O29" t="n">
         <v>-0.98</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43109</v>
+        <v>43110</v>
       </c>
       <c r="H30" t="n">
-        <v>2859.7</v>
+        <v>2809.75</v>
       </c>
       <c r="I30" t="n">
         <v>2824.389350245542</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.22</v>
+        <v>-8.84</v>
       </c>
       <c r="L30" t="n">
-        <v>7.81</v>
+        <v>9.16</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>8.02</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43171</v>
+        <v>43172</v>
       </c>
       <c r="H31" t="n">
-        <v>2831.7</v>
+        <v>2884.95</v>
       </c>
       <c r="I31" t="n">
         <v>2838.664961531792</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.78</v>
+        <v>-2.68</v>
       </c>
       <c r="L31" t="n">
-        <v>2.43</v>
+        <v>2.93</v>
       </c>
       <c r="M31" t="n">
         <v>1.23</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.59</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43223</v>
+        <v>43224</v>
       </c>
       <c r="H32" t="n">
-        <v>2987.85</v>
+        <v>2920.85</v>
       </c>
       <c r="I32" t="n">
         <v>2986.433665812068</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K32" t="n">
-        <v>3.57</v>
+        <v>1.24</v>
       </c>
       <c r="L32" t="n">
         <v>5.37</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.24</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43307</v>
+        <v>43308</v>
       </c>
       <c r="H33" t="n">
-        <v>2826.55</v>
+        <v>2894.6</v>
       </c>
       <c r="I33" t="n">
         <v>2865.907365746597</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K33" t="n">
-        <v>3.23</v>
+        <v>0.9</v>
       </c>
       <c r="L33" t="n">
         <v>7.84</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>8.18</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43364</v>
+        <v>43367</v>
       </c>
       <c r="H34" t="n">
-        <v>2794</v>
+        <v>2585.3</v>
       </c>
       <c r="I34" t="n">
         <v>2752.235427926113</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.48</v>
+        <v>-10.69</v>
       </c>
       <c r="L34" t="n">
-        <v>8.1</v>
+        <v>11.52</v>
       </c>
       <c r="M34" t="n">
         <v>2.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.78</v>
+        <v>7.47</v>
       </c>
       <c r="O34" t="n">
         <v>2.41</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>15.21</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43419</v>
+        <v>43420</v>
       </c>
       <c r="H35" t="n">
-        <v>2394.55</v>
+        <v>2473.5</v>
       </c>
       <c r="I35" t="n">
         <v>2441.436785721158</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K35" t="n">
-        <v>7.38</v>
+        <v>4.32</v>
       </c>
       <c r="L35" t="n">
         <v>8.69</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>13.16</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43439</v>
+        <v>43440</v>
       </c>
       <c r="H36" t="n">
-        <v>2279.35</v>
+        <v>2221.15</v>
       </c>
       <c r="I36" t="n">
         <v>2224.128225576454</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K36" t="n">
-        <v>-7.85</v>
+        <v>-10.2</v>
       </c>
       <c r="L36" t="n">
-        <v>8.289999999999999</v>
+        <v>10.65</v>
       </c>
       <c r="M36" t="n">
         <v>0.52</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>11.49</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43501</v>
+        <v>43502</v>
       </c>
       <c r="H37" t="n">
-        <v>2047.95</v>
+        <v>2110.4</v>
       </c>
       <c r="I37" t="n">
         <v>2049.346788377483</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K37" t="n">
-        <v>7.8</v>
+        <v>4.99</v>
       </c>
       <c r="L37" t="n">
         <v>9.039999999999999</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43552</v>
+        <v>43553</v>
       </c>
       <c r="H38" t="n">
-        <v>2089.9</v>
+        <v>2054.75</v>
       </c>
       <c r="I38" t="n">
         <v>2059.880838014423</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.97</v>
+        <v>-2.64</v>
       </c>
       <c r="L38" t="n">
         <v>8.449999999999999</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.99</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43601</v>
+        <v>43602</v>
       </c>
       <c r="H39" t="n">
-        <v>2030.5</v>
+        <v>2093.7</v>
       </c>
       <c r="I39" t="n">
         <v>2050.044056253765</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K39" t="n">
-        <v>1.18</v>
+        <v>-1.9</v>
       </c>
       <c r="L39" t="n">
         <v>4.93</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>11.48</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43637</v>
+        <v>43640</v>
       </c>
       <c r="H40" t="n">
-        <v>1971.9</v>
+        <v>1909.8</v>
       </c>
       <c r="I40" t="n">
         <v>1934.651592191905</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K40" t="n">
-        <v>-5.82</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>6.58</v>
+        <v>9.67</v>
       </c>
       <c r="M40" t="n">
         <v>0.8</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.73</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H41" t="n">
-        <v>1575.25</v>
+        <v>1786</v>
       </c>
       <c r="I41" t="n">
         <v>1732.384297735954</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K41" t="n">
-        <v>17.52</v>
+        <v>6.48</v>
       </c>
       <c r="L41" t="n">
         <v>6.24</v>
@@ -2778,7 +3269,7 @@
         <v>4.65</v>
       </c>
       <c r="N41" t="n">
-        <v>4.98</v>
+        <v>13.38</v>
       </c>
       <c r="O41" t="n">
         <v>-3.15</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>16.9</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>43804</v>
+        <v>43805</v>
       </c>
       <c r="H42" t="n">
-        <v>2141.7</v>
+        <v>2092</v>
       </c>
       <c r="I42" t="n">
         <v>2118.335093196758</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K42" t="n">
-        <v>19.92</v>
+        <v>17.13</v>
       </c>
       <c r="L42" t="n">
         <v>11.76</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.75</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>43978</v>
+        <v>43979</v>
       </c>
       <c r="H43" t="n">
-        <v>1496.7</v>
+        <v>1623.65</v>
       </c>
       <c r="I43" t="n">
         <v>1513.447912060661</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K43" t="n">
-        <v>28.46</v>
+        <v>22.39</v>
       </c>
       <c r="L43" t="n">
         <v>9.35</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>6</v>
+      </c>
+      <c r="U43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>17.41</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44134</v>
+        <v>44137</v>
       </c>
       <c r="H44" t="n">
-        <v>2085.6</v>
+        <v>2029.65</v>
       </c>
       <c r="I44" t="n">
         <v>2076.625352234657</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K44" t="n">
-        <v>28.45</v>
+        <v>25.01</v>
       </c>
       <c r="L44" t="n">
         <v>7.32</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>6</v>
+      </c>
+      <c r="U44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>10.89</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44145</v>
+        <v>44146</v>
       </c>
       <c r="H45" t="n">
-        <v>2234.85</v>
+        <v>2326.7</v>
       </c>
       <c r="I45" t="n">
         <v>2250.623016445085</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>-10.11</v>
+        <v>-14.64</v>
       </c>
       <c r="L45" t="n">
-        <v>11.22</v>
+        <v>14.95</v>
       </c>
       <c r="M45" t="n">
         <v>1.17</v>
       </c>
       <c r="N45" t="n">
-        <v>3.22</v>
+        <v>4.11</v>
       </c>
       <c r="O45" t="n">
         <v>-2.68</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.75</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44243</v>
+        <v>44244</v>
       </c>
       <c r="H46" t="n">
-        <v>2726.95</v>
+        <v>2695.5</v>
       </c>
       <c r="I46" t="n">
         <v>2703.790392140727</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K46" t="n">
-        <v>17.2</v>
+        <v>15.85</v>
       </c>
       <c r="L46" t="n">
         <v>4.51</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.4</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44333</v>
+        <v>44334</v>
       </c>
       <c r="H47" t="n">
-        <v>2484.35</v>
+        <v>2571.85</v>
       </c>
       <c r="I47" t="n">
         <v>2562.697655117615</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K47" t="n">
-        <v>7.83</v>
+        <v>4.59</v>
       </c>
       <c r="L47" t="n">
         <v>1.84</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.25</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H48" t="n">
-        <v>2579.75</v>
+        <v>2554.85</v>
       </c>
       <c r="I48" t="n">
         <v>2579.368301099237</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K48" t="n">
-        <v>0.31</v>
+        <v>-0.66</v>
       </c>
       <c r="L48" t="n">
         <v>3.08</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>6.68</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44412</v>
+        <v>44413</v>
       </c>
       <c r="H49" t="n">
-        <v>2641.8</v>
+        <v>2732.15</v>
       </c>
       <c r="I49" t="n">
         <v>2688.090209111362</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.4</v>
+        <v>-6.94</v>
       </c>
       <c r="L49" t="n">
-        <v>4.89</v>
+        <v>7.91</v>
       </c>
       <c r="M49" t="n">
         <v>1.18</v>
       </c>
       <c r="N49" t="n">
-        <v>2.86</v>
+        <v>3.42</v>
       </c>
       <c r="O49" t="n">
         <v>-0.97</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>7.82</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44420</v>
+        <v>44421</v>
       </c>
       <c r="H50" t="n">
-        <v>2616.55</v>
+        <v>2546.8</v>
       </c>
       <c r="I50" t="n">
         <v>2575.910121421831</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.23</v>
+        <v>-6.78</v>
       </c>
       <c r="L50" t="n">
-        <v>4.8</v>
+        <v>7.65</v>
       </c>
       <c r="M50" t="n">
-        <v>0.05</v>
+        <v>1.59</v>
       </c>
       <c r="N50" t="n">
         <v>3.74</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44440</v>
+        <v>44441</v>
       </c>
       <c r="H51" t="n">
-        <v>2703.15</v>
+        <v>2733.2</v>
       </c>
       <c r="I51" t="n">
         <v>2710.702277792814</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.14</v>
+        <v>-7.32</v>
       </c>
       <c r="L51" t="n">
         <v>8.65</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44488</v>
+        <v>44489</v>
       </c>
       <c r="H52" t="n">
-        <v>2703.7</v>
+        <v>2651.2</v>
       </c>
       <c r="I52" t="n">
         <v>2700.529579483826</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.08</v>
+        <v>-3</v>
       </c>
       <c r="L52" t="n">
-        <v>1.71</v>
+        <v>4.28</v>
       </c>
       <c r="M52" t="n">
         <v>1.46</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>10.22</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44509</v>
+        <v>44510</v>
       </c>
       <c r="H53" t="n">
-        <v>2724.25</v>
+        <v>2746.75</v>
       </c>
       <c r="I53" t="n">
         <v>2732.392099707129</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.76</v>
+        <v>-3.6</v>
       </c>
       <c r="L53" t="n">
         <v>4.75</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>9.01</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H54" t="n">
-        <v>2520.4</v>
+        <v>2433.9</v>
       </c>
       <c r="I54" t="n">
         <v>2499.281583138089</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-8.24</v>
+        <v>-11.39</v>
       </c>
       <c r="L54" t="n">
-        <v>9.09</v>
+        <v>11.84</v>
       </c>
       <c r="M54" t="n">
-        <v>0.61</v>
+        <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>2.65</v>
+        <v>3.43</v>
       </c>
       <c r="O54" t="n">
         <v>0.83</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>11.57</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44561</v>
+        <v>44564</v>
       </c>
       <c r="H55" t="n">
-        <v>2591.9</v>
+        <v>2718.8</v>
       </c>
       <c r="I55" t="n">
         <v>2606.234959603653</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.49</v>
+        <v>-11.71</v>
       </c>
       <c r="L55" t="n">
-        <v>7</v>
+        <v>12.31</v>
       </c>
       <c r="M55" t="n">
         <v>1.67</v>
       </c>
       <c r="N55" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="O55" t="n">
         <v>-3.43</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>9.73</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44586</v>
+        <v>44588</v>
       </c>
       <c r="H56" t="n">
-        <v>2692</v>
+        <v>2643.85</v>
       </c>
       <c r="I56" t="n">
         <v>2650.715544027869</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.99</v>
+        <v>-2.76</v>
       </c>
       <c r="L56" t="n">
-        <v>4.6</v>
+        <v>5.46</v>
       </c>
       <c r="M56" t="n">
         <v>1.29</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.75</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H57" t="n">
-        <v>2481.2</v>
+        <v>2508.95</v>
       </c>
       <c r="I57" t="n">
         <v>2504.220226137572</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K57" t="n">
-        <v>6.15</v>
+        <v>5.1</v>
       </c>
       <c r="L57" t="n">
         <v>4.5</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>10.15</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44685</v>
+        <v>44686</v>
       </c>
       <c r="H58" t="n">
-        <v>2483.2</v>
+        <v>2433.55</v>
       </c>
       <c r="I58" t="n">
         <v>2452.620461853517</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.03</v>
+        <v>-3.01</v>
       </c>
       <c r="L58" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="M58" t="n">
         <v>1.16</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>12.35</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44694</v>
+        <v>44697</v>
       </c>
       <c r="H59" t="n">
-        <v>2432.65</v>
+        <v>2617.95</v>
       </c>
       <c r="I59" t="n">
         <v>2590.809482682105</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>0.04</v>
+        <v>-7.58</v>
       </c>
       <c r="L59" t="n">
-        <v>3.93</v>
+        <v>8.01</v>
       </c>
       <c r="M59" t="n">
-        <v>0.64</v>
+        <v>3.59</v>
       </c>
       <c r="N59" t="n">
-        <v>3.04</v>
+        <v>7.62</v>
       </c>
       <c r="O59" t="n">
         <v>-2</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>13.18</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44844</v>
+        <v>44845</v>
       </c>
       <c r="H60" t="n">
-        <v>3531.6</v>
+        <v>3408</v>
       </c>
       <c r="I60" t="n">
         <v>3415.14111882597</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K60" t="n">
-        <v>34.9</v>
+        <v>30.18</v>
       </c>
       <c r="L60" t="n">
         <v>4.71</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>6</v>
+      </c>
+      <c r="U60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>12.83</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>44862</v>
+        <v>44865</v>
       </c>
       <c r="H61" t="n">
-        <v>3745.75</v>
+        <v>3850.45</v>
       </c>
       <c r="I61" t="n">
         <v>3786.546856049979</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>-9.91</v>
+        <v>-12.98</v>
       </c>
       <c r="L61" t="n">
-        <v>10.71</v>
+        <v>13.38</v>
       </c>
       <c r="M61" t="n">
         <v>2.12</v>
       </c>
       <c r="N61" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O61" t="n">
         <v>-3.5</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>44879</v>
+        <v>44880</v>
       </c>
       <c r="H62" t="n">
-        <v>3516.6</v>
+        <v>3507.95</v>
       </c>
       <c r="I62" t="n">
         <v>3515.008236762624</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K62" t="n">
-        <v>-8.67</v>
+        <v>-8.9</v>
       </c>
       <c r="L62" t="n">
         <v>9.15</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.69</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45026</v>
+        <v>45027</v>
       </c>
       <c r="H63" t="n">
-        <v>2970.45</v>
+        <v>3054.2</v>
       </c>
       <c r="I63" t="n">
         <v>3054.035262451411</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K63" t="n">
-        <v>15.32</v>
+        <v>12.93</v>
       </c>
       <c r="L63" t="n">
         <v>2.16</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>6</v>
+      </c>
+      <c r="U63" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.81</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45093</v>
+        <v>45096</v>
       </c>
       <c r="H64" t="n">
-        <v>3538.9</v>
+        <v>3496.65</v>
       </c>
       <c r="I64" t="n">
         <v>3527.206420859809</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K64" t="n">
-        <v>15.87</v>
+        <v>14.49</v>
       </c>
       <c r="L64" t="n">
         <v>2.74</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.99</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45194</v>
+        <v>45195</v>
       </c>
       <c r="H65" t="n">
-        <v>3386.65</v>
+        <v>3472.15</v>
       </c>
       <c r="I65" t="n">
         <v>3464.558774764274</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K65" t="n">
-        <v>3.15</v>
+        <v>0.7</v>
       </c>
       <c r="L65" t="n">
         <v>4.84</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.64</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H66" t="n">
-        <v>3384.4</v>
+        <v>3326.8</v>
       </c>
       <c r="I66" t="n">
         <v>3340.35435980121</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.53</v>
+        <v>-4.19</v>
       </c>
       <c r="L66" t="n">
         <v>4.87</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,25 +5042,25 @@
         <v>6.02</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45233</v>
+        <v>45236</v>
       </c>
       <c r="H67" t="n">
-        <v>3428</v>
+        <v>3510.95</v>
       </c>
       <c r="I67" t="n">
         <v>3489.792365032758</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.04</v>
+        <v>-5.54</v>
       </c>
       <c r="L67" t="n">
-        <v>3.95</v>
+        <v>6.51</v>
       </c>
       <c r="M67" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="N67" t="n">
         <v>2.69</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.97</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45300</v>
+        <v>45301</v>
       </c>
       <c r="H68" t="n">
-        <v>3870.45</v>
+        <v>3842.55</v>
       </c>
       <c r="I68" t="n">
         <v>3844.893795665302</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K68" t="n">
-        <v>10.24</v>
+        <v>9.44</v>
       </c>
       <c r="L68" t="n">
         <v>2.09</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>6.65</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="H69" t="n">
-        <v>3839.6</v>
+        <v>3933.2</v>
       </c>
       <c r="I69" t="n">
         <v>3878.902753725451</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K69" t="n">
-        <v>0.08</v>
+        <v>-2.36</v>
       </c>
       <c r="L69" t="n">
-        <v>2.14</v>
+        <v>3.21</v>
       </c>
       <c r="M69" t="n">
         <v>1.24</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H70" t="n">
-        <v>4670.85</v>
+        <v>4495.4</v>
       </c>
       <c r="I70" t="n">
         <v>4533.794422691687</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K70" t="n">
-        <v>18.75</v>
+        <v>14.29</v>
       </c>
       <c r="L70" t="n">
         <v>6.64</v>
@@ -4431,7 +5270,7 @@
         <v>1.21</v>
       </c>
       <c r="N70" t="n">
-        <v>3.47</v>
+        <v>3.76</v>
       </c>
       <c r="O70" t="n">
         <v>2.44</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>5</v>
+      </c>
+      <c r="U70" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>9.19</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H71" t="n">
-        <v>4801.5</v>
+        <v>4935.1</v>
       </c>
       <c r="I71" t="n">
         <v>4908.336565119277</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.81</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>8.77</v>
+        <v>10</v>
       </c>
       <c r="M71" t="n">
         <v>0.97</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H72" t="n">
-        <v>4675.75</v>
+        <v>4653.9</v>
       </c>
       <c r="I72" t="n">
         <v>4659.685565274322</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.26</v>
+        <v>-5.7</v>
       </c>
       <c r="L72" t="n">
         <v>7.7</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45533</v>
+        <v>45534</v>
       </c>
       <c r="H73" t="n">
-        <v>4915.9</v>
+        <v>4960.5</v>
       </c>
       <c r="I73" t="n">
         <v>4956.990163880049</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K73" t="n">
-        <v>-5.63</v>
+        <v>-6.59</v>
       </c>
       <c r="L73" t="n">
         <v>7.32</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>6.11</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H74" t="n">
-        <v>4782.5</v>
+        <v>4706.8</v>
       </c>
       <c r="I74" t="n">
         <v>4744.785230683007</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.59</v>
+        <v>-5.11</v>
       </c>
       <c r="L74" t="n">
         <v>5.47</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,25 +5594,25 @@
         <v>8.15</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45596</v>
+        <v>45597</v>
       </c>
       <c r="H75" t="n">
-        <v>4894.65</v>
+        <v>4953.6</v>
       </c>
       <c r="I75" t="n">
         <v>4926.739057214297</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.99</v>
+        <v>-5.24</v>
       </c>
       <c r="L75" t="n">
-        <v>5.12</v>
+        <v>6.02</v>
       </c>
       <c r="M75" t="n">
-        <v>0.89</v>
+        <v>1.84</v>
       </c>
       <c r="N75" t="n">
         <v>3.76</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>7.46</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45698</v>
+        <v>45699</v>
       </c>
       <c r="H76" t="n">
-        <v>5335.35</v>
+        <v>4972.35</v>
       </c>
       <c r="I76" t="n">
         <v>5088.563559789753</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K76" t="n">
-        <v>7.71</v>
+        <v>0.38</v>
       </c>
       <c r="L76" t="n">
         <v>8.43</v>
       </c>
       <c r="M76" t="n">
-        <v>1.51</v>
+        <v>3.68</v>
       </c>
       <c r="N76" t="n">
-        <v>3.16</v>
+        <v>6.8</v>
       </c>
       <c r="O76" t="n">
         <v>1.2</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>10.77</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H77" t="n">
-        <v>5100.9</v>
+        <v>5229.35</v>
       </c>
       <c r="I77" t="n">
         <v>5144.345473739849</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K77" t="n">
-        <v>-2.59</v>
+        <v>-5.17</v>
       </c>
       <c r="L77" t="n">
-        <v>3.47</v>
+        <v>5.76</v>
       </c>
       <c r="M77" t="n">
         <v>1.12</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>7.83</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H78" t="n">
-        <v>5247.9</v>
+        <v>5065.25</v>
       </c>
       <c r="I78" t="n">
         <v>5089.35221237826</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K78" t="n">
-        <v>0.35</v>
+        <v>-3.14</v>
       </c>
       <c r="L78" t="n">
-        <v>2.22</v>
+        <v>4.39</v>
       </c>
       <c r="M78" t="n">
-        <v>1.69</v>
+        <v>4.72</v>
       </c>
       <c r="N78" t="n">
-        <v>2.44</v>
+        <v>3.48</v>
       </c>
       <c r="O78" t="n">
         <v>2.52</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>8.69</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H79" t="n">
-        <v>5350.9</v>
+        <v>5529</v>
       </c>
       <c r="I79" t="n">
         <v>5505.580625365452</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K79" t="n">
-        <v>-5.64</v>
+        <v>-9.16</v>
       </c>
       <c r="L79" t="n">
-        <v>6.79</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M79" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="N79" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="O79" t="n">
         <v>-3.48</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45784</v>
+        <v>45785</v>
       </c>
       <c r="H80" t="n">
-        <v>5489</v>
+        <v>5372.5</v>
       </c>
       <c r="I80" t="n">
         <v>5380.034063358128</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.72</v>
+        <v>-2.83</v>
       </c>
       <c r="L80" t="n">
-        <v>2.77</v>
+        <v>3.43</v>
       </c>
       <c r="M80" t="n">
         <v>0.99</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>8.82</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45831</v>
+        <v>45832</v>
       </c>
       <c r="H81" t="n">
-        <v>5552.5</v>
+        <v>5629</v>
       </c>
       <c r="I81" t="n">
         <v>5565.460250443896</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K81" t="n">
-        <v>-3.35</v>
+        <v>-4.77</v>
       </c>
       <c r="L81" t="n">
-        <v>4.76</v>
+        <v>4.97</v>
       </c>
       <c r="M81" t="n">
         <v>3.4</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,28 +6077,28 @@
         <v>5.49</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="H82" t="n">
-        <v>5558</v>
+        <v>5439.5</v>
       </c>
       <c r="I82" t="n">
         <v>5470.926167757601</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K82" t="n">
-        <v>-1.26</v>
+        <v>-3.37</v>
       </c>
       <c r="L82" t="n">
-        <v>2.08</v>
+        <v>3.47</v>
       </c>
       <c r="M82" t="n">
-        <v>0.54</v>
+        <v>1.58</v>
       </c>
       <c r="N82" t="n">
-        <v>1.52</v>
+        <v>2.13</v>
       </c>
       <c r="O82" t="n">
         <v>1.38</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,22 +6146,22 @@
         <v>5.62</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>45873</v>
+        <v>45874</v>
       </c>
       <c r="H83" t="n">
-        <v>5621</v>
+        <v>5681</v>
       </c>
       <c r="I83" t="n">
         <v>5660.374792984365</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K83" t="n">
-        <v>-3.34</v>
+        <v>-4.44</v>
       </c>
       <c r="L83" t="n">
-        <v>4.24</v>
+        <v>4.61</v>
       </c>
       <c r="M83" t="n">
         <v>1.51</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,28 +6215,28 @@
         <v>6.56</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="H84" t="n">
-        <v>6855</v>
+        <v>6695</v>
       </c>
       <c r="I84" t="n">
         <v>6706.15458523226</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K84" t="n">
-        <v>20.67</v>
+        <v>17.85</v>
       </c>
       <c r="L84" t="n">
         <v>1.7</v>
       </c>
       <c r="M84" t="n">
-        <v>0.58</v>
+        <v>0.82</v>
       </c>
       <c r="N84" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="O84" t="n">
         <v>1.07</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>4</v>
+      </c>
+      <c r="U84" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -5265,22 +6284,22 @@
         <v>7.24</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H85" t="n">
-        <v>7134.5</v>
+        <v>7258.5</v>
       </c>
       <c r="I85" t="n">
         <v>7159.988997364104</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K85" t="n">
-        <v>-6.56</v>
+        <v>-8.42</v>
       </c>
       <c r="L85" t="n">
-        <v>7.62</v>
+        <v>8.81</v>
       </c>
       <c r="M85" t="n">
         <v>0.53</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S85" t="b">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -5322,19 +6353,19 @@
         <v>6.69</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H86" t="n">
-        <v>7323.5</v>
+        <v>7173.5</v>
       </c>
       <c r="I86" t="n">
         <v>7220.501043113435</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K86" t="n">
-        <v>0.9</v>
+        <v>-1.17</v>
       </c>
       <c r="L86" t="n">
         <v>4.17</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>3</v>
+      </c>
+      <c r="U86" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -5379,28 +6422,28 @@
         <v>6.96</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H87" t="n">
-        <v>7296</v>
+        <v>7771</v>
       </c>
       <c r="I87" t="n">
         <v>7489.55517491725</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K87" t="n">
-        <v>-1.71</v>
+        <v>-8.33</v>
       </c>
       <c r="L87" t="n">
-        <v>2.81</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M87" t="n">
         <v>3.07</v>
       </c>
       <c r="N87" t="n">
-        <v>3.29</v>
+        <v>6.51</v>
       </c>
       <c r="O87" t="n">
         <v>-2.05</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5436,28 +6491,28 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H88" t="n">
-        <v>7620.5</v>
+        <v>7266</v>
       </c>
       <c r="I88" t="n">
         <v>7548.464633477333</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K88" t="n">
-        <v>-1.94</v>
+        <v>-6.5</v>
       </c>
       <c r="L88" t="n">
-        <v>3.47</v>
+        <v>6.87</v>
       </c>
       <c r="M88" t="n">
         <v>2.63</v>
       </c>
       <c r="N88" t="n">
-        <v>2.55</v>
+        <v>4.65</v>
       </c>
       <c r="O88" t="n">
         <v>6.51</v>
@@ -5466,7 +6521,19 @@
         <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>2</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -5493,19 +6560,19 @@
         <v>10.67</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H89" t="n">
-        <v>7147.5</v>
+        <v>7424</v>
       </c>
       <c r="I89" t="n">
         <v>7242.685940372705</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K89" t="n">
-        <v>1.63</v>
+        <v>-2.17</v>
       </c>
       <c r="L89" t="n">
         <v>4.24</v>
@@ -5523,7 +6590,19 @@
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5550,19 +6629,19 @@
         <v>11.75</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="H90" t="n">
-        <v>7426</v>
+        <v>7073.5</v>
       </c>
       <c r="I90" t="n">
         <v>7175.266835576612</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K90" t="n">
-        <v>0.03</v>
+        <v>-4.72</v>
       </c>
       <c r="L90" t="n">
         <v>9.039999999999999</v>
@@ -5580,7 +6659,19 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>3</v>
+      </c>
+      <c r="U90" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -5607,22 +6698,22 @@
         <v>9.91</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="H91" t="n">
-        <v>7563.5</v>
+        <v>7689.5</v>
       </c>
       <c r="I91" t="n">
         <v>7684.701976864651</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K91" t="n">
-        <v>-6.93</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L91" t="n">
-        <v>7.49</v>
+        <v>9</v>
       </c>
       <c r="M91" t="n">
         <v>1.79</v>
@@ -5637,7 +6728,19 @@
         <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S91" t="b">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5664,28 +6767,28 @@
         <v>6.59</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="H92" t="n">
-        <v>7970</v>
+        <v>7711.5</v>
       </c>
       <c r="I92" t="n">
         <v>7716.965361442208</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K92" t="n">
-        <v>3.65</v>
+        <v>0.29</v>
       </c>
       <c r="L92" t="n">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="M92" t="n">
-        <v>0.73</v>
+        <v>1.38</v>
       </c>
       <c r="N92" t="n">
-        <v>1.43</v>
+        <v>3.24</v>
       </c>
       <c r="O92" t="n">
         <v>1.67</v>
@@ -5694,7 +6797,19 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S92" t="b">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>3</v>
+      </c>
+      <c r="U92" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -5721,19 +6836,19 @@
         <v>6.1</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H93" t="n">
-        <v>7225</v>
+        <v>7284.5</v>
       </c>
       <c r="I93" t="n">
         <v>7273.456450027081</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K93" t="n">
-        <v>6.31</v>
+        <v>5.54</v>
       </c>
       <c r="L93" t="n">
         <v>2.35</v>
@@ -5751,7 +6866,19 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S93" t="b">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>2</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -5802,6 +6929,14 @@
       <c r="Q94" t="n">
         <v>8</v>
       </c>
+      <c r="R94" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S94" t="b">
+        <v>1</v>
+      </c>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10760,7 +11895,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45.1</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="6">
@@ -10770,7 +11905,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -10780,7 +11915,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8">
@@ -10790,7 +11925,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -10800,7 +11935,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -10810,7 +11945,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>97.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -10820,7 +11955,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -10830,7 +11965,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -10840,7 +11975,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="14">
@@ -10850,7 +11985,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="15">
@@ -10860,7 +11995,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.47</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="16">
@@ -10870,7 +12005,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.47</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="17">
@@ -10880,7 +12015,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34.9</v>
+        <v>30.18</v>
       </c>
     </row>
     <row r="18">
@@ -10890,7 +12025,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.6</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="19">
@@ -10900,7 +12035,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.65</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="20">
@@ -10910,7 +12045,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.03</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="21">
@@ -10920,7 +12055,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.7</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="22">
@@ -10930,7 +12065,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
@@ -10940,7 +12075,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -10950,7 +12085,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="25">
@@ -10970,7 +12105,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.76</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="27">
@@ -10980,7 +12115,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.46</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="28">
@@ -10990,7 +12125,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
